--- a/docs/data/jp/xlsx/3969.xlsx
+++ b/docs/data/jp/xlsx/3969.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC142"/>
+  <dimension ref="A1:AC148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4261,10 +4264,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>1390</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4299,7 +4304,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>7487400</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5498,7 +5505,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5750,506 +5757,564 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>181.13</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>190.764</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>201.699</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>239.903</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>222.469</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>229.002</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>234.225</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>243.933</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>266.661</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>261.105</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>267.983</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>292.48</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>131.342</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>119.59</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>201.699</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>234.225</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>267.983</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>451.755</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>448.561</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>487.273</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>401.969</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>512.722</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>458.547</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>467.472</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>451.93</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>442.829</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>495.299</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>473.024</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>496.29</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>415.633</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>424.399</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>487.273</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>467.472</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>473.024</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>175.57</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>178.656</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>190.143</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>188.398</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>196.7</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>234.666</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>162.747</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>228.895</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>183.075</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>207.915</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>193.323</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>241.612</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>183.841</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>147.079</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>190.143</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>162.747</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>193.323</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>276.185</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>269.905</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>297.13</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>213.571</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>316.021</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>223.882</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>304.725</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>223.034</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>259.755</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>287.383</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>279.701</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>254.678</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>231.792</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>277.319</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>297.13</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>304.725</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>279.701</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
+          <t>판매비와 관리비</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="n">
+        <v>175.57</v>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>178.656</v>
+      </c>
+      <c r="E83" s="22" t="n">
+        <v>190.143</v>
+      </c>
+      <c r="F83" s="22" t="n">
+        <v>188.398</v>
+      </c>
+      <c r="G83" s="22" t="n">
+        <v>196.7</v>
+      </c>
+      <c r="H83" s="22" t="n">
+        <v>234.666</v>
+      </c>
+      <c r="I83" s="22" t="n">
+        <v>162.747</v>
+      </c>
+      <c r="J83" s="22" t="n">
+        <v>228.895</v>
+      </c>
+      <c r="K83" s="22" t="n">
+        <v>183.075</v>
+      </c>
+      <c r="L83" s="22" t="n">
+        <v>207.915</v>
+      </c>
+      <c r="M83" s="22" t="n">
+        <v>193.323</v>
+      </c>
+      <c r="N83" s="22" t="n">
+        <v>241.612</v>
+      </c>
+      <c r="T83" s="22" t="n">
+        <v>183.841</v>
+      </c>
+      <c r="U83" s="22" t="n">
+        <v>147.079</v>
+      </c>
+      <c r="V83" s="22" t="n">
+        <v>190.143</v>
+      </c>
+      <c r="W83" s="22" t="n">
+        <v>162.747</v>
+      </c>
+      <c r="X83" s="22" t="n">
+        <v>193.323</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>276.185</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>269.905</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>297.13</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>213.571</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>316.021</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>223.882</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>304.725</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>223.034</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>259.755</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>287.383</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>279.701</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>254.678</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>231.792</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>277.319</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>297.13</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>304.725</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>279.701</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
           <t>이자·배당금 수익</t>
         </is>
       </c>
-      <c r="D83" s="22" t="n">
+      <c r="D87" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E83" s="22" t="n">
+      <c r="E87" s="22" t="n">
         <v>0.021</v>
       </c>
-      <c r="H83" s="22" t="n">
+      <c r="H87" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="22" t="n">
+      <c r="I87" s="22" t="n">
         <v>2.271</v>
       </c>
-      <c r="L83" s="22" t="n">
+      <c r="L87" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T83" s="22" t="n">
+      <c r="T87" s="22" t="n">
         <v>0.018</v>
       </c>
-      <c r="U83" s="22" t="n">
+      <c r="U87" s="22" t="n">
         <v>0.019</v>
       </c>
-      <c r="V83" s="22" t="n">
+      <c r="V87" s="22" t="n">
         <v>0.021</v>
       </c>
-      <c r="W83" s="22" t="n">
+      <c r="W87" s="22" t="n">
         <v>2.271</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>이자수익</t>
-        </is>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>4.615</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T85" s="22" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>3.521</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>4.763</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>6.688</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>4.615</v>
-      </c>
-      <c r="T86" s="22" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>0.371</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>3.521</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>6.688</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C87" s="12" t="n">
-        <v>276.244</v>
-      </c>
-      <c r="D87" s="12" t="n">
-        <v>269.905</v>
-      </c>
-      <c r="E87" s="12" t="n">
-        <v>300.651</v>
-      </c>
-      <c r="F87" s="12" t="n">
-        <v>213.586</v>
-      </c>
-      <c r="G87" s="12" t="n">
-        <v>316.419</v>
-      </c>
-      <c r="H87" s="12" t="n">
-        <v>223.915</v>
-      </c>
-      <c r="I87" s="12" t="n">
-        <v>306.996</v>
-      </c>
-      <c r="J87" s="12" t="n">
-        <v>223.034</v>
-      </c>
-      <c r="K87" s="12" t="n">
-        <v>264.518</v>
-      </c>
-      <c r="L87" s="12" t="n">
-        <v>287.465</v>
-      </c>
-      <c r="M87" s="12" t="n">
-        <v>286.39</v>
-      </c>
-      <c r="N87" s="12" t="n">
-        <v>259.293</v>
-      </c>
-      <c r="T87" s="12" t="n">
-        <v>232.5</v>
-      </c>
-      <c r="U87" s="12" t="n">
-        <v>277.69</v>
-      </c>
-      <c r="V87" s="12" t="n">
-        <v>300.651</v>
-      </c>
-      <c r="W87" s="12" t="n">
-        <v>306.996</v>
-      </c>
-      <c r="X87" s="12" t="n">
-        <v>286.39</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 환입이익</t>
-        </is>
-      </c>
-      <c r="C88" s="22" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="D88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="22" t="n">
-        <v>0</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="J88" s="22" t="n">
         <v>0</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="U88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W88" s="22" t="n">
-        <v>0</v>
+        <v>4.615</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>특별이익 합계</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>0.314</v>
+        <v>0.038</v>
       </c>
       <c r="D89" s="22" t="n">
         <v>0</v>
@@ -6258,13 +6323,13 @@
         <v>0</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="G89" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="I89" s="22" t="n">
         <v>0</v>
@@ -6272,11 +6337,20 @@
       <c r="J89" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="N89" s="22" t="n">
-        <v>0.98</v>
+      <c r="K89" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="22" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="M89" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" s="22" t="n">
+        <v>0.6889999999999999</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>0</v>
+        <v>0.351</v>
       </c>
       <c r="V89" s="22" t="n">
         <v>0</v>
@@ -6284,2166 +6358,2499 @@
       <c r="W89" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="X89" s="22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C90" s="12" t="n">
-        <v>276.559</v>
-      </c>
-      <c r="D90" s="12" t="n">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>3.521</v>
+      </c>
+      <c r="F90" s="22" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G90" s="22" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="H90" s="22" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="I90" s="22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="22" t="n">
+        <v>4.763</v>
+      </c>
+      <c r="L90" s="22" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="M90" s="22" t="n">
+        <v>6.688</v>
+      </c>
+      <c r="N90" s="22" t="n">
+        <v>4.615</v>
+      </c>
+      <c r="T90" s="22" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="U90" s="22" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="V90" s="22" t="n">
+        <v>3.521</v>
+      </c>
+      <c r="W90" s="22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="X90" s="22" t="n">
+        <v>6.688</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="n">
+        <v>276.244</v>
+      </c>
+      <c r="D91" s="12" t="n">
         <v>269.905</v>
       </c>
-      <c r="E90" s="12" t="n">
-        <v>300.65</v>
-      </c>
-      <c r="F90" s="12" t="n">
+      <c r="E91" s="12" t="n">
+        <v>300.651</v>
+      </c>
+      <c r="F91" s="12" t="n">
         <v>213.586</v>
       </c>
-      <c r="G90" s="12" t="n">
+      <c r="G91" s="12" t="n">
         <v>316.419</v>
       </c>
-      <c r="H90" s="12" t="n">
+      <c r="H91" s="12" t="n">
         <v>223.915</v>
       </c>
-      <c r="I90" s="12" t="n">
+      <c r="I91" s="12" t="n">
         <v>306.996</v>
       </c>
-      <c r="J90" s="12" t="n">
+      <c r="J91" s="12" t="n">
         <v>223.034</v>
       </c>
-      <c r="K90" s="12" t="n">
+      <c r="K91" s="12" t="n">
         <v>264.518</v>
       </c>
-      <c r="L90" s="12" t="n">
+      <c r="L91" s="12" t="n">
         <v>287.465</v>
       </c>
-      <c r="M90" s="12" t="n">
-        <v>293.157</v>
-      </c>
-      <c r="N90" s="12" t="n">
-        <v>260.274</v>
-      </c>
-      <c r="T90" s="12" t="n">
+      <c r="M91" s="12" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="N91" s="12" t="n">
+        <v>259.293</v>
+      </c>
+      <c r="T91" s="12" t="n">
         <v>232.5</v>
       </c>
-      <c r="U90" s="12" t="n">
+      <c r="U91" s="12" t="n">
         <v>277.69</v>
       </c>
-      <c r="V90" s="12" t="n">
-        <v>300.65</v>
-      </c>
-      <c r="W90" s="12" t="n">
+      <c r="V91" s="12" t="n">
+        <v>300.651</v>
+      </c>
+      <c r="W91" s="12" t="n">
         <v>306.996</v>
       </c>
-      <c r="X90" s="12" t="n">
-        <v>293.157</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="20" t="inlineStr">
-        <is>
-          <t>법인세·주민세·사업세</t>
-        </is>
-      </c>
-      <c r="C91" s="22" t="n">
-        <v>104.055</v>
-      </c>
-      <c r="D91" s="22" t="n">
-        <v>77.121</v>
-      </c>
-      <c r="E91" s="22" t="n">
-        <v>110.263</v>
-      </c>
-      <c r="F91" s="22" t="n">
-        <v>57.066</v>
-      </c>
-      <c r="G91" s="22" t="n">
-        <v>120.379</v>
-      </c>
-      <c r="H91" s="22" t="n">
-        <v>60.161</v>
-      </c>
-      <c r="I91" s="22" t="n">
-        <v>82.093</v>
-      </c>
-      <c r="J91" s="22" t="n">
-        <v>64.721</v>
-      </c>
-      <c r="K91" s="22" t="n">
-        <v>99.254</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>80.245</v>
-      </c>
-      <c r="M91" s="22" t="n">
-        <v>112.694</v>
-      </c>
-      <c r="N91" s="22" t="n">
-        <v>81.065</v>
-      </c>
-      <c r="T91" s="22" t="n">
-        <v>92.18300000000001</v>
-      </c>
-      <c r="U91" s="22" t="n">
-        <v>98.82599999999999</v>
-      </c>
-      <c r="V91" s="22" t="n">
-        <v>110.263</v>
-      </c>
-      <c r="W91" s="22" t="n">
-        <v>82.093</v>
-      </c>
-      <c r="X91" s="22" t="n">
-        <v>112.694</v>
+      <c r="X91" s="12" t="n">
+        <v>286.39</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="20" t="inlineStr">
-        <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C92" s="22" t="n">
-        <v>-15.024</v>
-      </c>
-      <c r="D92" s="22" t="n">
-        <v>12.235</v>
-      </c>
-      <c r="E92" s="22" t="n">
-        <v>-18.006</v>
-      </c>
-      <c r="F92" s="22" t="n">
-        <v>16.63</v>
-      </c>
-      <c r="G92" s="22" t="n">
-        <v>-18.506</v>
-      </c>
-      <c r="H92" s="22" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="I92" s="22" t="n">
-        <v>-2.481</v>
-      </c>
-      <c r="J92" s="22" t="n">
-        <v>15.875</v>
-      </c>
-      <c r="K92" s="22" t="n">
-        <v>-15.135</v>
-      </c>
-      <c r="L92" s="22" t="n">
-        <v>17.238</v>
-      </c>
-      <c r="M92" s="22" t="n">
-        <v>-22.793</v>
-      </c>
-      <c r="N92" s="22" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="T92" s="22" t="n">
-        <v>-14.507</v>
-      </c>
-      <c r="U92" s="22" t="n">
-        <v>-11.066</v>
-      </c>
-      <c r="V92" s="22" t="n">
-        <v>-18.006</v>
-      </c>
-      <c r="W92" s="22" t="n">
-        <v>-2.481</v>
-      </c>
-      <c r="X92" s="22" t="n">
-        <v>-22.793</v>
+      <c r="A92" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G92" s="17">
+        <f>IF(OR(G91="",C91=""),"",IF(C91&lt;=0,"",IFERROR(G91/C91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H92" s="17">
+        <f>IF(OR(H91="",D91=""),"",IF(D91&lt;=0,"",IFERROR(H91/D91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I92" s="17">
+        <f>IF(OR(I91="",E91=""),"",IF(E91&lt;=0,"",IFERROR(I91/E91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J92" s="17">
+        <f>IF(OR(J91="",F91=""),"",IF(F91&lt;=0,"",IFERROR(J91/F91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K92" s="17">
+        <f>IF(OR(K91="",G91=""),"",IF(G91&lt;=0,"",IFERROR(K91/G91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L92" s="17">
+        <f>IF(OR(L91="",H91=""),"",IF(H91&lt;=0,"",IFERROR(L91/H91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M92" s="17">
+        <f>IF(OR(M91="",I91=""),"",IF(I91&lt;=0,"",IFERROR(M91/I91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N92" s="17">
+        <f>IF(OR(N91="",J91=""),"",IF(J91&lt;=0,"",IFERROR(N91/J91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T92" s="17">
+        <f>IF(OR(T91="",S91=""),"",IF(S91&lt;=0,"",IFERROR(T91/S91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U92" s="17">
+        <f>IF(OR(U91="",T91=""),"",IF(T91&lt;=0,"",IFERROR(U91/T91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V92" s="17">
+        <f>IF(OR(V91="",U91=""),"",IF(U91&lt;=0,"",IFERROR(V91/U91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W92" s="17">
+        <f>IF(OR(W91="",V91=""),"",IF(V91&lt;=0,"",IFERROR(W91/V91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X92" s="17">
+        <f>IF(OR(X91="",W91=""),"",IF(W91&lt;=0,"",IFERROR(X91/W91-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
+          <t>신주예약권 환입이익</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="D93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="22" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="U93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>특별이익 합계</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="D94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="22" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="U94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="n">
+        <v>276.559</v>
+      </c>
+      <c r="D95" s="12" t="n">
+        <v>269.905</v>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>300.65</v>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>213.586</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>316.419</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>223.915</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <v>306.996</v>
+      </c>
+      <c r="J95" s="12" t="n">
+        <v>223.034</v>
+      </c>
+      <c r="K95" s="12" t="n">
+        <v>264.518</v>
+      </c>
+      <c r="L95" s="12" t="n">
+        <v>287.465</v>
+      </c>
+      <c r="M95" s="12" t="n">
+        <v>293.157</v>
+      </c>
+      <c r="N95" s="12" t="n">
+        <v>260.274</v>
+      </c>
+      <c r="T95" s="12" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="U95" s="12" t="n">
+        <v>277.69</v>
+      </c>
+      <c r="V95" s="12" t="n">
+        <v>300.65</v>
+      </c>
+      <c r="W95" s="12" t="n">
+        <v>306.996</v>
+      </c>
+      <c r="X95" s="12" t="n">
+        <v>293.157</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C96" s="22" t="n">
+        <v>104.055</v>
+      </c>
+      <c r="D96" s="22" t="n">
+        <v>77.121</v>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>110.263</v>
+      </c>
+      <c r="F96" s="22" t="n">
+        <v>57.066</v>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>120.379</v>
+      </c>
+      <c r="H96" s="22" t="n">
+        <v>60.161</v>
+      </c>
+      <c r="I96" s="22" t="n">
+        <v>82.093</v>
+      </c>
+      <c r="J96" s="22" t="n">
+        <v>64.721</v>
+      </c>
+      <c r="K96" s="22" t="n">
+        <v>99.254</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>80.245</v>
+      </c>
+      <c r="M96" s="22" t="n">
+        <v>112.694</v>
+      </c>
+      <c r="N96" s="22" t="n">
+        <v>81.065</v>
+      </c>
+      <c r="T96" s="22" t="n">
+        <v>92.18300000000001</v>
+      </c>
+      <c r="U96" s="22" t="n">
+        <v>98.82599999999999</v>
+      </c>
+      <c r="V96" s="22" t="n">
+        <v>110.263</v>
+      </c>
+      <c r="W96" s="22" t="n">
+        <v>82.093</v>
+      </c>
+      <c r="X96" s="22" t="n">
+        <v>112.694</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C97" s="22" t="n">
+        <v>-15.024</v>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>12.235</v>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>-18.006</v>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="G97" s="22" t="n">
+        <v>-18.506</v>
+      </c>
+      <c r="H97" s="22" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="I97" s="22" t="n">
+        <v>-2.481</v>
+      </c>
+      <c r="J97" s="22" t="n">
+        <v>15.875</v>
+      </c>
+      <c r="K97" s="22" t="n">
+        <v>-15.135</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <v>17.238</v>
+      </c>
+      <c r="M97" s="22" t="n">
+        <v>-22.793</v>
+      </c>
+      <c r="N97" s="22" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="T97" s="22" t="n">
+        <v>-14.507</v>
+      </c>
+      <c r="U97" s="22" t="n">
+        <v>-11.066</v>
+      </c>
+      <c r="V97" s="22" t="n">
+        <v>-18.006</v>
+      </c>
+      <c r="W97" s="22" t="n">
+        <v>-2.481</v>
+      </c>
+      <c r="X97" s="22" t="n">
+        <v>-22.793</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
           <t>법인세 등 합계</t>
         </is>
       </c>
-      <c r="C93" s="22" t="n">
+      <c r="C98" s="22" t="n">
         <v>89.03100000000001</v>
       </c>
-      <c r="D93" s="22" t="n">
+      <c r="D98" s="22" t="n">
         <v>89.357</v>
       </c>
-      <c r="E93" s="22" t="n">
+      <c r="E98" s="22" t="n">
         <v>92.256</v>
       </c>
-      <c r="F93" s="22" t="n">
+      <c r="F98" s="22" t="n">
         <v>73.696</v>
       </c>
-      <c r="G93" s="22" t="n">
+      <c r="G98" s="22" t="n">
         <v>101.872</v>
       </c>
-      <c r="H93" s="22" t="n">
+      <c r="H98" s="22" t="n">
         <v>77.392</v>
       </c>
-      <c r="I93" s="22" t="n">
+      <c r="I98" s="22" t="n">
         <v>79.613</v>
       </c>
-      <c r="J93" s="22" t="n">
+      <c r="J98" s="22" t="n">
         <v>80.59699999999999</v>
       </c>
-      <c r="K93" s="22" t="n">
+      <c r="K98" s="22" t="n">
         <v>84.11799999999999</v>
       </c>
-      <c r="L93" s="22" t="n">
+      <c r="L98" s="22" t="n">
         <v>97.483</v>
       </c>
-      <c r="M93" s="22" t="n">
+      <c r="M98" s="22" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="N93" s="22" t="n">
+      <c r="N98" s="22" t="n">
         <v>93.455</v>
       </c>
-      <c r="T93" s="22" t="n">
+      <c r="T98" s="22" t="n">
         <v>77.675</v>
       </c>
-      <c r="U93" s="22" t="n">
+      <c r="U98" s="22" t="n">
         <v>87.76000000000001</v>
       </c>
-      <c r="V93" s="22" t="n">
+      <c r="V98" s="22" t="n">
         <v>92.256</v>
       </c>
-      <c r="W93" s="22" t="n">
+      <c r="W98" s="22" t="n">
         <v>79.613</v>
       </c>
-      <c r="X93" s="22" t="n">
+      <c r="X98" s="22" t="n">
         <v>89.90000000000001</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="9" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C94" s="12" t="n">
+      <c r="C99" s="12" t="n">
         <v>187.527</v>
       </c>
-      <c r="D94" s="12" t="n">
+      <c r="D99" s="12" t="n">
         <v>180.549</v>
       </c>
-      <c r="E94" s="12" t="n">
+      <c r="E99" s="12" t="n">
         <v>208.394</v>
       </c>
-      <c r="F94" s="12" t="n">
+      <c r="F99" s="12" t="n">
         <v>139.889</v>
       </c>
-      <c r="G94" s="12" t="n">
+      <c r="G99" s="12" t="n">
         <v>214.548</v>
       </c>
-      <c r="H94" s="12" t="n">
+      <c r="H99" s="12" t="n">
         <v>146.523</v>
       </c>
-      <c r="I94" s="12" t="n">
+      <c r="I99" s="12" t="n">
         <v>227.382</v>
       </c>
-      <c r="J94" s="12" t="n">
+      <c r="J99" s="12" t="n">
         <v>142.436</v>
       </c>
-      <c r="K94" s="12" t="n">
+      <c r="K99" s="12" t="n">
         <v>180.4</v>
       </c>
-      <c r="L94" s="12" t="n">
+      <c r="L99" s="12" t="n">
         <v>189.982</v>
       </c>
-      <c r="M94" s="12" t="n">
+      <c r="M99" s="12" t="n">
         <v>203.257</v>
       </c>
-      <c r="N94" s="12" t="n">
+      <c r="N99" s="12" t="n">
         <v>166.819</v>
       </c>
-      <c r="T94" s="12" t="n">
+      <c r="T99" s="12" t="n">
         <v>154.824</v>
       </c>
-      <c r="U94" s="12" t="n">
+      <c r="U99" s="12" t="n">
         <v>189.93</v>
       </c>
-      <c r="V94" s="12" t="n">
+      <c r="V99" s="12" t="n">
         <v>208.394</v>
       </c>
-      <c r="W94" s="12" t="n">
+      <c r="W99" s="12" t="n">
         <v>227.382</v>
       </c>
-      <c r="X94" s="12" t="n">
+      <c r="X99" s="12" t="n">
         <v>203.257</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="18" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G100" s="17">
+        <f>IF(OR(G99="",C99=""),"",IF(C99&lt;=0,"",IFERROR(G99/C99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H100" s="17">
+        <f>IF(OR(H99="",D99=""),"",IF(D99&lt;=0,"",IFERROR(H99/D99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I100" s="17">
+        <f>IF(OR(I99="",E99=""),"",IF(E99&lt;=0,"",IFERROR(I99/E99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J100" s="17">
+        <f>IF(OR(J99="",F99=""),"",IF(F99&lt;=0,"",IFERROR(J99/F99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K100" s="17">
+        <f>IF(OR(K99="",G99=""),"",IF(G99&lt;=0,"",IFERROR(K99/G99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L100" s="17">
+        <f>IF(OR(L99="",H99=""),"",IF(H99&lt;=0,"",IFERROR(L99/H99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M100" s="17">
+        <f>IF(OR(M99="",I99=""),"",IF(I99&lt;=0,"",IFERROR(M99/I99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N100" s="17">
+        <f>IF(OR(N99="",J99=""),"",IF(J99&lt;=0,"",IFERROR(N99/J99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T100" s="17">
+        <f>IF(OR(T99="",S99=""),"",IF(S99&lt;=0,"",IFERROR(T99/S99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U100" s="17">
+        <f>IF(OR(U99="",T99=""),"",IF(T99&lt;=0,"",IFERROR(U99/T99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V100" s="17">
+        <f>IF(OR(V99="",U99=""),"",IF(U99&lt;=0,"",IFERROR(V99/U99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W100" s="17">
+        <f>IF(OR(W99="",V99=""),"",IF(V99&lt;=0,"",IFERROR(W99/V99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X100" s="17">
+        <f>IF(OR(X99="",W99=""),"",IF(W99&lt;=0,"",IFERROR(X99/W99-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B96" s="44" t="inlineStr">
+      <c r="B102" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C96" s="18" t="n"/>
-      <c r="D96" s="18" t="n"/>
-      <c r="E96" s="18" t="n"/>
-      <c r="F96" s="18" t="n"/>
-      <c r="G96" s="18" t="n"/>
-      <c r="H96" s="18" t="n"/>
-      <c r="I96" s="18" t="n"/>
-      <c r="J96" s="18" t="n"/>
-      <c r="K96" s="18" t="n"/>
-      <c r="L96" s="18" t="n"/>
-      <c r="M96" s="18" t="n"/>
-      <c r="N96" s="18" t="n"/>
-      <c r="O96" s="18" t="n"/>
-      <c r="P96" s="18" t="n"/>
-      <c r="Q96" s="18" t="n"/>
-      <c r="R96" s="18" t="n"/>
-      <c r="S96" s="18" t="n"/>
-      <c r="T96" s="18" t="n"/>
-      <c r="U96" s="18" t="n"/>
-      <c r="V96" s="18" t="n"/>
-      <c r="W96" s="18" t="n"/>
-      <c r="X96" s="18" t="n"/>
-      <c r="Y96" s="18" t="n"/>
-      <c r="Z96" s="18" t="n"/>
-      <c r="AA96" s="18" t="n"/>
-      <c r="AB96" s="18" t="n"/>
-      <c r="AC96" s="18" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="C102" s="18" t="n"/>
+      <c r="D102" s="18" t="n"/>
+      <c r="E102" s="18" t="n"/>
+      <c r="F102" s="18" t="n"/>
+      <c r="G102" s="18" t="n"/>
+      <c r="H102" s="18" t="n"/>
+      <c r="I102" s="18" t="n"/>
+      <c r="J102" s="18" t="n"/>
+      <c r="K102" s="18" t="n"/>
+      <c r="L102" s="18" t="n"/>
+      <c r="M102" s="18" t="n"/>
+      <c r="N102" s="18" t="n"/>
+      <c r="O102" s="18" t="n"/>
+      <c r="P102" s="18" t="n"/>
+      <c r="Q102" s="18" t="n"/>
+      <c r="R102" s="18" t="n"/>
+      <c r="S102" s="18" t="n"/>
+      <c r="T102" s="18" t="n"/>
+      <c r="U102" s="18" t="n"/>
+      <c r="V102" s="18" t="n"/>
+      <c r="W102" s="18" t="n"/>
+      <c r="X102" s="18" t="n"/>
+      <c r="Y102" s="18" t="n"/>
+      <c r="Z102" s="18" t="n"/>
+      <c r="AA102" s="18" t="n"/>
+      <c r="AB102" s="18" t="n"/>
+      <c r="AC102" s="18" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E103" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="F103" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G103" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="H103" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I103" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J97" s="5" t="inlineStr">
+      <c r="J103" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K97" s="5" t="inlineStr">
+      <c r="K103" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L97" s="5" t="inlineStr">
+      <c r="L103" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M97" s="5" t="inlineStr">
+      <c r="M103" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N97" s="5" t="inlineStr">
+      <c r="N103" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O97" s="5" t="inlineStr">
+      <c r="O103" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P97" s="5" t="inlineStr">
+      <c r="P103" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q97" s="5" t="inlineStr">
+      <c r="Q103" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R97" s="5" t="inlineStr">
+      <c r="R103" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S97" s="5" t="inlineStr">
+      <c r="S103" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T97" s="5" t="inlineStr">
+      <c r="T103" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U97" s="5" t="inlineStr">
+      <c r="U103" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V97" s="5" t="inlineStr">
+      <c r="V103" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W97" s="5" t="inlineStr">
+      <c r="W103" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X97" s="5" t="inlineStr">
+      <c r="X103" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y97" s="5" t="inlineStr">
+      <c r="Y103" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z97" s="5" t="inlineStr">
+      <c r="Z103" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA97" s="5" t="inlineStr">
+      <c r="AA103" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB97" s="5" t="inlineStr">
+      <c r="AB103" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC97" s="5" t="inlineStr">
+      <c r="AC103" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="9" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="C98" s="12" t="n">
+      <c r="C104" s="12" t="n">
         <v>483.742</v>
       </c>
-      <c r="E98" s="12" t="n">
+      <c r="E104" s="12" t="n">
         <v>1054.297</v>
       </c>
-      <c r="G98" s="12" t="n">
+      <c r="G104" s="12" t="n">
         <v>530.005</v>
       </c>
-      <c r="I98" s="12" t="n">
+      <c r="I104" s="12" t="n">
         <v>1060.916</v>
       </c>
-      <c r="K98" s="12" t="n">
+      <c r="K104" s="12" t="n">
         <v>487.552</v>
       </c>
-      <c r="M98" s="12" t="n">
+      <c r="M104" s="12" t="n">
         <v>1068.174</v>
       </c>
-      <c r="O98" s="12" t="n">
+      <c r="O104" s="12" t="n">
         <v>278.721</v>
       </c>
-      <c r="P98" s="12" t="n">
+      <c r="P104" s="12" t="n">
         <v>324.395</v>
       </c>
-      <c r="Q98" s="12" t="n">
+      <c r="Q104" s="12" t="n">
         <v>487.059</v>
       </c>
-      <c r="R98" s="12" t="n">
+      <c r="R104" s="12" t="n">
         <v>607.716</v>
       </c>
-      <c r="S98" s="12" t="n">
+      <c r="S104" s="12" t="n">
         <v>790.953</v>
       </c>
-      <c r="T98" s="12" t="n">
+      <c r="T104" s="12" t="n">
         <v>908.521</v>
       </c>
-      <c r="U98" s="12" t="n">
+      <c r="U104" s="12" t="n">
         <v>999.66</v>
       </c>
-      <c r="V98" s="12" t="n">
+      <c r="V104" s="12" t="n">
         <v>1054.297</v>
       </c>
-      <c r="W98" s="12" t="n">
+      <c r="W104" s="12" t="n">
         <v>1060.916</v>
       </c>
-      <c r="X98" s="12" t="n">
+      <c r="X104" s="12" t="n">
         <v>1068.174</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="C99" s="22" t="n">
-        <v>131.737</v>
-      </c>
-      <c r="E99" s="22" t="n">
-        <v>282.49</v>
-      </c>
-      <c r="G99" s="22" t="n">
-        <v>167.519</v>
-      </c>
-      <c r="I99" s="22" t="n">
-        <v>376.434</v>
-      </c>
-      <c r="K99" s="22" t="n">
-        <v>195.572</v>
-      </c>
-      <c r="M99" s="22" t="n">
-        <v>415.213</v>
-      </c>
-      <c r="O99" s="22" t="n">
-        <v>126.037</v>
-      </c>
-      <c r="P99" s="22" t="n">
-        <v>147.407</v>
-      </c>
-      <c r="Q99" s="22" t="n">
-        <v>159.388</v>
-      </c>
-      <c r="R99" s="22" t="n">
-        <v>187.371</v>
-      </c>
-      <c r="S99" s="22" t="n">
-        <v>163.572</v>
-      </c>
-      <c r="T99" s="22" t="n">
-        <v>186.06</v>
-      </c>
-      <c r="U99" s="22" t="n">
-        <v>222.148</v>
-      </c>
-      <c r="V99" s="22" t="n">
-        <v>282.49</v>
-      </c>
-      <c r="W99" s="22" t="n">
-        <v>376.434</v>
-      </c>
-      <c r="X99" s="22" t="n">
-        <v>415.213</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C100" s="22" t="n">
-        <v>5.595</v>
-      </c>
-      <c r="E100" s="22" t="n">
-        <v>17.331</v>
-      </c>
-      <c r="G100" s="22" t="n">
-        <v>5.531</v>
-      </c>
-      <c r="I100" s="22" t="n">
-        <v>11.348</v>
-      </c>
-      <c r="K100" s="22" t="n">
-        <v>-5.411</v>
-      </c>
-      <c r="M100" s="22" t="n">
-        <v>3.342</v>
-      </c>
-      <c r="O100" s="22" t="n">
-        <v>11.713</v>
-      </c>
-      <c r="P100" s="22" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="Q100" s="22" t="n">
-        <v>11.025</v>
-      </c>
-      <c r="R100" s="22" t="n">
-        <v>-6.365</v>
-      </c>
-      <c r="S100" s="22" t="n">
-        <v>-1.078</v>
-      </c>
-      <c r="T100" s="22" t="n">
-        <v>5.826</v>
-      </c>
-      <c r="U100" s="22" t="n">
-        <v>-8.487</v>
-      </c>
-      <c r="V100" s="22" t="n">
-        <v>17.331</v>
-      </c>
-      <c r="W100" s="22" t="n">
-        <v>11.348</v>
-      </c>
-      <c r="X100" s="22" t="n">
-        <v>3.342</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여충당금 증감액</t>
-        </is>
-      </c>
-      <c r="C101" s="22" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="E101" s="22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="G101" s="22" t="n">
-        <v>1.322</v>
-      </c>
-      <c r="I101" s="22" t="n">
-        <v>2.646</v>
-      </c>
-      <c r="K101" s="22" t="n">
-        <v>1.414</v>
-      </c>
-      <c r="M101" s="22" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="O101" s="22" t="n">
-        <v>20.31</v>
-      </c>
-      <c r="P101" s="22" t="n">
-        <v>16.628</v>
-      </c>
-      <c r="Q101" s="22" t="n">
-        <v>8.496</v>
-      </c>
-      <c r="R101" s="22" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="S101" s="22" t="n">
-        <v>-15.908</v>
-      </c>
-      <c r="T101" s="22" t="n">
-        <v>-0.849</v>
-      </c>
-      <c r="U101" s="22" t="n">
-        <v>-9.125999999999999</v>
-      </c>
-      <c r="V101" s="22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W101" s="22" t="n">
-        <v>2.646</v>
-      </c>
-      <c r="X101" s="22" t="n">
-        <v>3.629</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>임원 퇴직위로 충당금 증감</t>
-        </is>
-      </c>
-      <c r="C102" s="22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E102" s="22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G102" s="22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="I102" s="22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K102" s="22" t="n">
-        <v>-2.954</v>
-      </c>
-      <c r="M102" s="22" t="n">
-        <v>-0.904</v>
-      </c>
-      <c r="O102" s="22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P102" s="22" t="n">
-        <v>6.318</v>
-      </c>
-      <c r="Q102" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="R102" s="22" t="n">
-        <v>-9.167</v>
-      </c>
-      <c r="S102" s="22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T102" s="22" t="n">
-        <v>2.976</v>
-      </c>
-      <c r="U102" s="22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V102" s="22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W102" s="22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X102" s="22" t="n">
-        <v>-0.904</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>이자수익</t>
-        </is>
-      </c>
-      <c r="O103" s="22" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="P103" s="22" t="n">
-        <v>-0.012</v>
-      </c>
-      <c r="Q103" s="22" t="n">
-        <v>-0.014</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="C104" s="22" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="E104" s="22" t="n">
-        <v>-0.041</v>
-      </c>
-      <c r="G104" s="22" t="n">
-        <v>-0.397</v>
-      </c>
-      <c r="I104" s="22" t="n">
-        <v>-2.668</v>
-      </c>
-      <c r="K104" s="22" t="n">
-        <v>-4.763</v>
-      </c>
-      <c r="M104" s="22" t="n">
-        <v>-10.451</v>
-      </c>
-      <c r="Q104" s="22" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="R104" s="22" t="n">
-        <v>-1.334</v>
-      </c>
-      <c r="S104" s="22" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="T104" s="22" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="U104" s="22" t="n">
-        <v>-0.037</v>
-      </c>
-      <c r="V104" s="22" t="n">
-        <v>-0.041</v>
-      </c>
-      <c r="W104" s="22" t="n">
-        <v>-2.668</v>
-      </c>
-      <c r="X104" s="22" t="n">
-        <v>-10.451</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용</t>
-        </is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="n">
+        <v>131.737</v>
+      </c>
+      <c r="E105" s="22" t="n">
+        <v>282.49</v>
+      </c>
+      <c r="G105" s="22" t="n">
+        <v>167.519</v>
+      </c>
+      <c r="I105" s="22" t="n">
+        <v>376.434</v>
+      </c>
+      <c r="K105" s="22" t="n">
+        <v>195.572</v>
+      </c>
+      <c r="M105" s="22" t="n">
+        <v>415.213</v>
       </c>
       <c r="O105" s="22" t="n">
-        <v>10.162</v>
+        <v>126.037</v>
       </c>
       <c r="P105" s="22" t="n">
-        <v>0</v>
+        <v>147.407</v>
       </c>
       <c r="Q105" s="22" t="n">
-        <v>25.657</v>
+        <v>159.388</v>
       </c>
       <c r="R105" s="22" t="n">
-        <v>0</v>
+        <v>187.371</v>
+      </c>
+      <c r="S105" s="22" t="n">
+        <v>163.572</v>
+      </c>
+      <c r="T105" s="22" t="n">
+        <v>186.06</v>
+      </c>
+      <c r="U105" s="22" t="n">
+        <v>222.148</v>
+      </c>
+      <c r="V105" s="22" t="n">
+        <v>282.49</v>
+      </c>
+      <c r="W105" s="22" t="n">
+        <v>376.434</v>
+      </c>
+      <c r="X105" s="22" t="n">
+        <v>415.213</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
+          <t>상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="n">
+        <v>5.595</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>17.331</v>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>5.531</v>
+      </c>
+      <c r="I106" s="22" t="n">
+        <v>11.348</v>
+      </c>
+      <c r="K106" s="22" t="n">
+        <v>-5.411</v>
+      </c>
+      <c r="M106" s="22" t="n">
+        <v>3.342</v>
+      </c>
+      <c r="O106" s="22" t="n">
+        <v>11.713</v>
       </c>
       <c r="P106" s="22" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="Q106" s="22" t="n">
-        <v>2.288</v>
+        <v>11.025</v>
       </c>
       <c r="R106" s="22" t="n">
-        <v>0</v>
+        <v>-6.365</v>
+      </c>
+      <c r="S106" s="22" t="n">
+        <v>-1.078</v>
+      </c>
+      <c r="T106" s="22" t="n">
+        <v>5.826</v>
+      </c>
+      <c r="U106" s="22" t="n">
+        <v>-8.487</v>
+      </c>
+      <c r="V106" s="22" t="n">
+        <v>17.331</v>
+      </c>
+      <c r="W106" s="22" t="n">
+        <v>11.348</v>
+      </c>
+      <c r="X106" s="22" t="n">
+        <v>3.342</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
-        </is>
+          <t>퇴직급여충당금 증감액</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>2.646</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>1.414</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="O107" s="22" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="P107" s="22" t="n">
+        <v>16.628</v>
       </c>
       <c r="Q107" s="22" t="n">
-        <v>0</v>
+        <v>8.496</v>
       </c>
       <c r="R107" s="22" t="n">
-        <v>-19.428</v>
+        <v>6.27</v>
       </c>
       <c r="S107" s="22" t="n">
-        <v>0</v>
+        <v>-15.908</v>
+      </c>
+      <c r="T107" s="22" t="n">
+        <v>-0.849</v>
+      </c>
+      <c r="U107" s="22" t="n">
+        <v>-9.125999999999999</v>
+      </c>
+      <c r="V107" s="22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>2.646</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>3.629</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="20" t="inlineStr">
         <is>
-          <t>주식보상비용</t>
+          <t>임원 퇴직위로 충당금 증감</t>
         </is>
       </c>
       <c r="C108" s="22" t="n">
-        <v>8.526</v>
+        <v>1.65</v>
       </c>
       <c r="E108" s="22" t="n">
-        <v>19.126</v>
+        <v>3.7</v>
       </c>
       <c r="G108" s="22" t="n">
-        <v>10.6</v>
+        <v>2.05</v>
       </c>
       <c r="I108" s="22" t="n">
-        <v>21.2</v>
+        <v>4.1</v>
       </c>
       <c r="K108" s="22" t="n">
-        <v>11.442</v>
+        <v>-2.954</v>
       </c>
       <c r="M108" s="22" t="n">
-        <v>11.442</v>
+        <v>-0.904</v>
+      </c>
+      <c r="O108" s="22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P108" s="22" t="n">
+        <v>6.318</v>
+      </c>
+      <c r="Q108" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="R108" s="22" t="n">
+        <v>-9.167</v>
       </c>
       <c r="S108" s="22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T108" s="22" t="n">
-        <v>15</v>
+        <v>2.976</v>
       </c>
       <c r="U108" s="22" t="n">
-        <v>18</v>
+        <v>2.5</v>
       </c>
       <c r="V108" s="22" t="n">
-        <v>19.126</v>
+        <v>3.7</v>
       </c>
       <c r="W108" s="22" t="n">
-        <v>21.2</v>
+        <v>4.1</v>
       </c>
       <c r="X108" s="22" t="n">
-        <v>11.442</v>
+        <v>-0.904</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 환입이익</t>
-        </is>
-      </c>
-      <c r="C109" s="22" t="n">
-        <v>-0.628</v>
-      </c>
-      <c r="E109" s="22" t="n">
-        <v>-0.628</v>
-      </c>
-      <c r="G109" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="22" t="n">
-        <v>-6.767</v>
-      </c>
-      <c r="U109" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V109" s="22" t="n">
-        <v>-0.628</v>
-      </c>
-      <c r="W109" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X109" s="22" t="n">
-        <v>-6.767</v>
+          <t>이자수익</t>
+        </is>
+      </c>
+      <c r="O109" s="22" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="P109" s="22" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="Q109" s="22" t="n">
+        <v>-0.014</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="C110" s="22" t="n">
-        <v>-19.165</v>
+        <v>-0.02</v>
       </c>
       <c r="E110" s="22" t="n">
-        <v>-86.372</v>
+        <v>-0.041</v>
       </c>
       <c r="G110" s="22" t="n">
-        <v>-31.362</v>
+        <v>-0.397</v>
       </c>
       <c r="I110" s="22" t="n">
-        <v>5.119</v>
+        <v>-2.668</v>
       </c>
       <c r="K110" s="22" t="n">
-        <v>68.354</v>
+        <v>-4.763</v>
       </c>
       <c r="M110" s="22" t="n">
-        <v>35.132</v>
-      </c>
-      <c r="O110" s="22" t="n">
-        <v>63.541</v>
-      </c>
-      <c r="P110" s="22" t="n">
-        <v>-9.285</v>
+        <v>-10.451</v>
       </c>
       <c r="Q110" s="22" t="n">
-        <v>-46.661</v>
+        <v>-0.014</v>
       </c>
       <c r="R110" s="22" t="n">
-        <v>9.51</v>
+        <v>-1.334</v>
       </c>
       <c r="S110" s="22" t="n">
-        <v>-149.142</v>
+        <v>-0.028</v>
       </c>
       <c r="T110" s="22" t="n">
-        <v>111.893</v>
+        <v>-0.033</v>
       </c>
       <c r="U110" s="22" t="n">
-        <v>-27.58</v>
+        <v>-0.037</v>
       </c>
       <c r="V110" s="22" t="n">
-        <v>-86.372</v>
+        <v>-0.041</v>
       </c>
       <c r="W110" s="22" t="n">
-        <v>5.119</v>
+        <v>-2.668</v>
       </c>
       <c r="X110" s="22" t="n">
-        <v>35.132</v>
+        <v>-10.451</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="C111" s="22" t="n">
-        <v>16.951</v>
-      </c>
-      <c r="E111" s="22" t="n">
-        <v>12.716</v>
-      </c>
-      <c r="G111" s="22" t="n">
-        <v>-2.453</v>
-      </c>
-      <c r="I111" s="22" t="n">
-        <v>-6.264</v>
-      </c>
-      <c r="K111" s="22" t="n">
-        <v>4.357</v>
-      </c>
-      <c r="M111" s="22" t="n">
-        <v>1.584</v>
+          <t>상장 관련 비용</t>
+        </is>
       </c>
       <c r="O111" s="22" t="n">
-        <v>-3.415</v>
+        <v>10.162</v>
       </c>
       <c r="P111" s="22" t="n">
-        <v>1.328</v>
+        <v>0</v>
       </c>
       <c r="Q111" s="22" t="n">
-        <v>6.326</v>
+        <v>25.657</v>
       </c>
       <c r="R111" s="22" t="n">
-        <v>14.601</v>
-      </c>
-      <c r="S111" s="22" t="n">
-        <v>2.152</v>
-      </c>
-      <c r="T111" s="22" t="n">
-        <v>3.457</v>
-      </c>
-      <c r="U111" s="22" t="n">
-        <v>-6.447</v>
-      </c>
-      <c r="V111" s="22" t="n">
-        <v>12.716</v>
-      </c>
-      <c r="W111" s="22" t="n">
-        <v>-6.264</v>
-      </c>
-      <c r="X111" s="22" t="n">
-        <v>1.584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>선수수익 증감</t>
-        </is>
-      </c>
-      <c r="O112" s="22" t="n">
-        <v>-18.847</v>
+          <t>고정자산 제각손실</t>
+        </is>
       </c>
       <c r="P112" s="22" t="n">
-        <v>37.513</v>
+        <v>0</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>62.559</v>
+        <v>2.288</v>
       </c>
       <c r="R112" s="22" t="n">
-        <v>76.693</v>
-      </c>
-      <c r="S112" s="22" t="n">
-        <v>57.905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
-        </is>
+          <t>투자유가증권 매각손익</t>
+        </is>
+      </c>
+      <c r="Q113" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" s="22" t="n">
+        <v>-19.428</v>
       </c>
       <c r="S113" s="22" t="n">
-        <v>57.905</v>
-      </c>
-      <c r="T113" s="22" t="n">
-        <v>66.32599999999999</v>
-      </c>
-      <c r="U113" s="22" t="n">
-        <v>18.552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
+          <t>주식보상비용</t>
         </is>
       </c>
       <c r="C114" s="22" t="n">
-        <v>23.434</v>
+        <v>8.526</v>
+      </c>
+      <c r="E114" s="22" t="n">
+        <v>19.126</v>
+      </c>
+      <c r="G114" s="22" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I114" s="22" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="K114" s="22" t="n">
+        <v>11.442</v>
+      </c>
+      <c r="M114" s="22" t="n">
+        <v>11.442</v>
+      </c>
+      <c r="S114" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="U114" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="V114" s="22" t="n">
+        <v>19.126</v>
+      </c>
+      <c r="W114" s="22" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="X114" s="22" t="n">
+        <v>11.442</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
+          <t>신주예약권 환입이익</t>
         </is>
       </c>
       <c r="C115" s="22" t="n">
-        <v>23.434</v>
+        <v>-0.628</v>
       </c>
       <c r="E115" s="22" t="n">
-        <v>56.99</v>
+        <v>-0.628</v>
       </c>
       <c r="G115" s="22" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="I115" s="22" t="n">
-        <v>71.828</v>
-      </c>
-      <c r="K115" s="22" t="n">
-        <v>-29.395</v>
+        <v>0</v>
       </c>
       <c r="M115" s="22" t="n">
-        <v>102.892</v>
+        <v>-6.767</v>
       </c>
       <c r="U115" s="22" t="n">
-        <v>18.552</v>
+        <v>0</v>
       </c>
       <c r="V115" s="22" t="n">
-        <v>56.99</v>
+        <v>-0.628</v>
       </c>
       <c r="W115" s="22" t="n">
-        <v>71.828</v>
+        <v>0</v>
       </c>
       <c r="X115" s="22" t="n">
-        <v>102.892</v>
+        <v>-6.767</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>미지급금 증감</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="C116" s="22" t="n">
-        <v>0.425</v>
+        <v>-19.165</v>
       </c>
       <c r="E116" s="22" t="n">
-        <v>14.497</v>
+        <v>-86.372</v>
       </c>
       <c r="G116" s="22" t="n">
-        <v>16.274</v>
+        <v>-31.362</v>
       </c>
       <c r="I116" s="22" t="n">
-        <v>35.048</v>
+        <v>5.119</v>
       </c>
       <c r="K116" s="22" t="n">
-        <v>-0.732</v>
+        <v>68.354</v>
       </c>
       <c r="M116" s="22" t="n">
-        <v>-1.361</v>
+        <v>35.132</v>
       </c>
       <c r="O116" s="22" t="n">
-        <v>1.168</v>
+        <v>63.541</v>
       </c>
       <c r="P116" s="22" t="n">
-        <v>-3.972</v>
+        <v>-9.285</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>20.798</v>
+        <v>-46.661</v>
       </c>
       <c r="R116" s="22" t="n">
-        <v>-7.026</v>
+        <v>9.51</v>
       </c>
       <c r="S116" s="22" t="n">
-        <v>25.055</v>
+        <v>-149.142</v>
       </c>
       <c r="T116" s="22" t="n">
-        <v>-12.665</v>
+        <v>111.893</v>
       </c>
       <c r="U116" s="22" t="n">
-        <v>-30.588</v>
+        <v>-27.58</v>
       </c>
       <c r="V116" s="22" t="n">
-        <v>14.497</v>
+        <v>-86.372</v>
       </c>
       <c r="W116" s="22" t="n">
-        <v>35.048</v>
+        <v>5.119</v>
       </c>
       <c r="X116" s="22" t="n">
-        <v>-1.361</v>
+        <v>35.132</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="C117" s="22" t="n">
-        <v>21.166</v>
+        <v>16.951</v>
       </c>
       <c r="E117" s="22" t="n">
-        <v>24.844</v>
+        <v>12.716</v>
       </c>
       <c r="G117" s="22" t="n">
-        <v>-3.77</v>
+        <v>-2.453</v>
       </c>
       <c r="I117" s="22" t="n">
-        <v>-24.504</v>
+        <v>-6.264</v>
       </c>
       <c r="K117" s="22" t="n">
-        <v>3.644</v>
+        <v>4.357</v>
       </c>
       <c r="M117" s="22" t="n">
-        <v>10.474</v>
+        <v>1.584</v>
       </c>
       <c r="O117" s="22" t="n">
-        <v>45.042</v>
+        <v>-3.415</v>
       </c>
       <c r="P117" s="22" t="n">
-        <v>-2.653</v>
+        <v>1.328</v>
       </c>
       <c r="Q117" s="22" t="n">
-        <v>21.102</v>
+        <v>6.326</v>
       </c>
       <c r="R117" s="22" t="n">
-        <v>-21.114</v>
+        <v>14.601</v>
       </c>
       <c r="S117" s="22" t="n">
-        <v>2.868</v>
+        <v>2.152</v>
       </c>
       <c r="T117" s="22" t="n">
-        <v>-9.51</v>
+        <v>3.457</v>
       </c>
       <c r="U117" s="22" t="n">
-        <v>-12.621</v>
+        <v>-6.447</v>
       </c>
       <c r="V117" s="22" t="n">
-        <v>24.844</v>
+        <v>12.716</v>
       </c>
       <c r="W117" s="22" t="n">
-        <v>-24.504</v>
+        <v>-6.264</v>
       </c>
       <c r="X117" s="22" t="n">
-        <v>10.474</v>
+        <v>1.584</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
-        </is>
-      </c>
-      <c r="C118" s="22" t="n">
-        <v>674.189</v>
-      </c>
-      <c r="E118" s="22" t="n">
-        <v>1400.682</v>
-      </c>
-      <c r="G118" s="22" t="n">
-        <v>731.7190000000001</v>
-      </c>
-      <c r="I118" s="22" t="n">
-        <v>1555.204</v>
-      </c>
-      <c r="K118" s="22" t="n">
-        <v>729.081</v>
-      </c>
-      <c r="M118" s="22" t="n">
-        <v>1632.401</v>
+          <t>선수수익 증감</t>
+        </is>
       </c>
       <c r="O118" s="22" t="n">
-        <v>539.926</v>
+        <v>-18.847</v>
       </c>
       <c r="P118" s="22" t="n">
-        <v>517.681</v>
+        <v>37.513</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>764.025</v>
+        <v>62.559</v>
       </c>
       <c r="R118" s="22" t="n">
-        <v>837.727</v>
+        <v>76.693</v>
       </c>
       <c r="S118" s="22" t="n">
-        <v>880.75</v>
-      </c>
-      <c r="T118" s="22" t="n">
-        <v>1277.003</v>
-      </c>
-      <c r="U118" s="22" t="n">
-        <v>1165.972</v>
-      </c>
-      <c r="V118" s="22" t="n">
-        <v>1400.682</v>
-      </c>
-      <c r="W118" s="22" t="n">
-        <v>1555.204</v>
-      </c>
-      <c r="X118" s="22" t="n">
-        <v>1632.401</v>
+        <v>57.905</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
-        </is>
-      </c>
-      <c r="C119" s="22" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G119" s="22" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="K119" s="22" t="n">
-        <v>4.763</v>
+          <t>계약부채 증감</t>
+        </is>
+      </c>
+      <c r="S119" s="22" t="n">
+        <v>57.905</v>
+      </c>
+      <c r="T119" s="22" t="n">
+        <v>66.32599999999999</v>
+      </c>
+      <c r="U119" s="22" t="n">
+        <v>18.552</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>이자 수취</t>
-        </is>
-      </c>
-      <c r="E120" s="22" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="I120" s="22" t="n">
-        <v>2.668</v>
-      </c>
-      <c r="M120" s="22" t="n">
-        <v>10.248</v>
-      </c>
-      <c r="O120" s="22" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="P120" s="22" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="Q120" s="22" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="R120" s="22" t="n">
-        <v>1.332</v>
-      </c>
-      <c r="S120" s="22" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="T120" s="22" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="U120" s="22" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="V120" s="22" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="W120" s="22" t="n">
-        <v>2.668</v>
-      </c>
-      <c r="X120" s="22" t="n">
-        <v>10.248</v>
+          <t>계약부채 증감</t>
+        </is>
+      </c>
+      <c r="C120" s="22" t="n">
+        <v>23.434</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>계약부채 증감</t>
         </is>
       </c>
       <c r="C121" s="22" t="n">
-        <v>-160.544</v>
+        <v>23.434</v>
       </c>
       <c r="E121" s="22" t="n">
-        <v>-318.13</v>
+        <v>56.99</v>
       </c>
       <c r="G121" s="22" t="n">
-        <v>-189.456</v>
+        <v>36.4</v>
       </c>
       <c r="I121" s="22" t="n">
-        <v>-363.293</v>
+        <v>71.828</v>
       </c>
       <c r="K121" s="22" t="n">
-        <v>-148.037</v>
+        <v>-29.395</v>
       </c>
       <c r="M121" s="22" t="n">
-        <v>-309.276</v>
-      </c>
-      <c r="O121" s="22" t="n">
-        <v>-34.084</v>
-      </c>
-      <c r="P121" s="22" t="n">
-        <v>-134.569</v>
-      </c>
-      <c r="Q121" s="22" t="n">
-        <v>-121.031</v>
-      </c>
-      <c r="R121" s="22" t="n">
-        <v>-229.332</v>
-      </c>
-      <c r="S121" s="22" t="n">
-        <v>-205.207</v>
-      </c>
-      <c r="T121" s="22" t="n">
-        <v>-291.911</v>
+        <v>102.892</v>
       </c>
       <c r="U121" s="22" t="n">
-        <v>-336.209</v>
+        <v>18.552</v>
       </c>
       <c r="V121" s="22" t="n">
-        <v>-318.13</v>
+        <v>56.99</v>
       </c>
       <c r="W121" s="22" t="n">
-        <v>-363.293</v>
+        <v>71.828</v>
       </c>
       <c r="X121" s="22" t="n">
-        <v>-309.276</v>
+        <v>102.892</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>Payments Of Head Office Relocation Expenses Ope CF</t>
-        </is>
+          <t>미지급금 증감</t>
+        </is>
+      </c>
+      <c r="C122" s="22" t="n">
+        <v>0.425</v>
       </c>
       <c r="E122" s="22" t="n">
-        <v>0</v>
+        <v>14.497</v>
+      </c>
+      <c r="G122" s="22" t="n">
+        <v>16.274</v>
       </c>
       <c r="I122" s="22" t="n">
-        <v>-45.591</v>
+        <v>35.048</v>
+      </c>
+      <c r="K122" s="22" t="n">
+        <v>-0.732</v>
       </c>
       <c r="M122" s="22" t="n">
-        <v>0</v>
+        <v>-1.361</v>
+      </c>
+      <c r="O122" s="22" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="P122" s="22" t="n">
+        <v>-3.972</v>
+      </c>
+      <c r="Q122" s="22" t="n">
+        <v>20.798</v>
+      </c>
+      <c r="R122" s="22" t="n">
+        <v>-7.026</v>
+      </c>
+      <c r="S122" s="22" t="n">
+        <v>25.055</v>
+      </c>
+      <c r="T122" s="22" t="n">
+        <v>-12.665</v>
+      </c>
+      <c r="U122" s="22" t="n">
+        <v>-30.588</v>
       </c>
       <c r="V122" s="22" t="n">
-        <v>0</v>
+        <v>14.497</v>
       </c>
       <c r="W122" s="22" t="n">
-        <v>-45.591</v>
+        <v>35.048</v>
       </c>
       <c r="X122" s="22" t="n">
-        <v>0</v>
+        <v>-1.361</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C123" s="12" t="n">
-        <v>513.6660000000001</v>
-      </c>
-      <c r="E123" s="12" t="n">
-        <v>1082.593</v>
-      </c>
-      <c r="G123" s="12" t="n">
-        <v>542.66</v>
-      </c>
-      <c r="I123" s="12" t="n">
-        <v>1148.987</v>
-      </c>
-      <c r="K123" s="12" t="n">
-        <v>585.807</v>
-      </c>
-      <c r="M123" s="12" t="n">
-        <v>1333.374</v>
-      </c>
-      <c r="O123" s="12" t="n">
-        <v>505.849</v>
-      </c>
-      <c r="P123" s="12" t="n">
-        <v>383.124</v>
-      </c>
-      <c r="Q123" s="12" t="n">
-        <v>643.008</v>
-      </c>
-      <c r="R123" s="12" t="n">
-        <v>609.727</v>
-      </c>
-      <c r="S123" s="12" t="n">
-        <v>675.571</v>
-      </c>
-      <c r="T123" s="12" t="n">
-        <v>985.125</v>
-      </c>
-      <c r="U123" s="12" t="n">
-        <v>829.8</v>
-      </c>
-      <c r="V123" s="12" t="n">
-        <v>1082.593</v>
-      </c>
-      <c r="W123" s="12" t="n">
-        <v>1148.987</v>
-      </c>
-      <c r="X123" s="12" t="n">
-        <v>1333.374</v>
+      <c r="A123" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C123" s="22" t="n">
+        <v>21.166</v>
+      </c>
+      <c r="E123" s="22" t="n">
+        <v>24.844</v>
+      </c>
+      <c r="G123" s="22" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="I123" s="22" t="n">
+        <v>-24.504</v>
+      </c>
+      <c r="K123" s="22" t="n">
+        <v>3.644</v>
+      </c>
+      <c r="M123" s="22" t="n">
+        <v>10.474</v>
+      </c>
+      <c r="O123" s="22" t="n">
+        <v>45.042</v>
+      </c>
+      <c r="P123" s="22" t="n">
+        <v>-2.653</v>
+      </c>
+      <c r="Q123" s="22" t="n">
+        <v>21.102</v>
+      </c>
+      <c r="R123" s="22" t="n">
+        <v>-21.114</v>
+      </c>
+      <c r="S123" s="22" t="n">
+        <v>2.868</v>
+      </c>
+      <c r="T123" s="22" t="n">
+        <v>-9.51</v>
+      </c>
+      <c r="U123" s="22" t="n">
+        <v>-12.621</v>
+      </c>
+      <c r="V123" s="22" t="n">
+        <v>24.844</v>
+      </c>
+      <c r="W123" s="22" t="n">
+        <v>-24.504</v>
+      </c>
+      <c r="X123" s="22" t="n">
+        <v>10.474</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="C124" s="22" t="n">
-        <v>-1.6</v>
+        <v>674.189</v>
       </c>
       <c r="E124" s="22" t="n">
-        <v>-1.797</v>
+        <v>1400.682</v>
       </c>
       <c r="G124" s="22" t="n">
-        <v>-1.743</v>
+        <v>731.7190000000001</v>
       </c>
       <c r="I124" s="22" t="n">
-        <v>-3.173</v>
+        <v>1555.204</v>
       </c>
       <c r="K124" s="22" t="n">
-        <v>-2.864</v>
+        <v>729.081</v>
       </c>
       <c r="M124" s="22" t="n">
-        <v>-4.075</v>
+        <v>1632.401</v>
       </c>
       <c r="O124" s="22" t="n">
-        <v>-1.443</v>
+        <v>539.926</v>
       </c>
       <c r="P124" s="22" t="n">
-        <v>0</v>
+        <v>517.681</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>-1.537</v>
+        <v>764.025</v>
       </c>
       <c r="R124" s="22" t="n">
-        <v>-0.237</v>
+        <v>837.727</v>
       </c>
       <c r="S124" s="22" t="n">
-        <v>-7.487</v>
+        <v>880.75</v>
       </c>
       <c r="T124" s="22" t="n">
-        <v>0</v>
+        <v>1277.003</v>
       </c>
       <c r="U124" s="22" t="n">
-        <v>-11.778</v>
+        <v>1165.972</v>
       </c>
       <c r="V124" s="22" t="n">
-        <v>-1.797</v>
+        <v>1400.682</v>
       </c>
       <c r="W124" s="22" t="n">
-        <v>-3.173</v>
+        <v>1555.204</v>
       </c>
       <c r="X124" s="22" t="n">
-        <v>-4.075</v>
+        <v>1632.401</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="C125" s="22" t="n">
-        <v>-218.557</v>
-      </c>
-      <c r="E125" s="22" t="n">
-        <v>-448.281</v>
+        <v>0.02</v>
       </c>
       <c r="G125" s="22" t="n">
-        <v>-221.224</v>
-      </c>
-      <c r="I125" s="22" t="n">
-        <v>-451.285</v>
+        <v>0.397</v>
       </c>
       <c r="K125" s="22" t="n">
-        <v>-268.712</v>
-      </c>
-      <c r="M125" s="22" t="n">
-        <v>-541.332</v>
-      </c>
-      <c r="O125" s="22" t="n">
-        <v>-161.439</v>
-      </c>
-      <c r="P125" s="22" t="n">
-        <v>-143.21</v>
-      </c>
-      <c r="Q125" s="22" t="n">
-        <v>-128.894</v>
-      </c>
-      <c r="R125" s="22" t="n">
-        <v>-207.595</v>
-      </c>
-      <c r="S125" s="22" t="n">
-        <v>-181.156</v>
-      </c>
-      <c r="T125" s="22" t="n">
-        <v>-199.425</v>
-      </c>
-      <c r="U125" s="22" t="n">
-        <v>-335.02</v>
-      </c>
-      <c r="V125" s="22" t="n">
-        <v>-448.281</v>
-      </c>
-      <c r="W125" s="22" t="n">
-        <v>-451.285</v>
-      </c>
-      <c r="X125" s="22" t="n">
-        <v>-541.332</v>
+        <v>4.763</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 납입</t>
-        </is>
+          <t>이자 수취</t>
+        </is>
+      </c>
+      <c r="E126" s="22" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="I126" s="22" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="M126" s="22" t="n">
+        <v>10.248</v>
       </c>
       <c r="O126" s="22" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="P126" s="22" t="n">
-        <v>0</v>
+        <v>0.012</v>
+      </c>
+      <c r="Q126" s="22" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="R126" s="22" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="S126" s="22" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="T126" s="22" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="U126" s="22" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="V126" s="22" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="W126" s="22" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="X126" s="22" t="n">
+        <v>10.248</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
-        </is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="C127" s="22" t="n">
+        <v>-160.544</v>
+      </c>
+      <c r="E127" s="22" t="n">
+        <v>-318.13</v>
+      </c>
+      <c r="G127" s="22" t="n">
+        <v>-189.456</v>
+      </c>
+      <c r="I127" s="22" t="n">
+        <v>-363.293</v>
+      </c>
+      <c r="K127" s="22" t="n">
+        <v>-148.037</v>
+      </c>
+      <c r="M127" s="22" t="n">
+        <v>-309.276</v>
+      </c>
+      <c r="O127" s="22" t="n">
+        <v>-34.084</v>
+      </c>
+      <c r="P127" s="22" t="n">
+        <v>-134.569</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>0</v>
+        <v>-121.031</v>
       </c>
       <c r="R127" s="22" t="n">
-        <v>-496.973</v>
+        <v>-229.332</v>
       </c>
       <c r="S127" s="22" t="n">
-        <v>0</v>
+        <v>-205.207</v>
+      </c>
+      <c r="T127" s="22" t="n">
+        <v>-291.911</v>
+      </c>
+      <c r="U127" s="22" t="n">
+        <v>-336.209</v>
+      </c>
+      <c r="V127" s="22" t="n">
+        <v>-318.13</v>
+      </c>
+      <c r="W127" s="22" t="n">
+        <v>-363.293</v>
+      </c>
+      <c r="X127" s="22" t="n">
+        <v>-309.276</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
-        </is>
-      </c>
-      <c r="Q128" s="22" t="n">
+          <t>Payments Of Head Office Relocation Expenses Ope CF</t>
+        </is>
+      </c>
+      <c r="E128" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R128" s="22" t="n">
-        <v>516.402</v>
-      </c>
-      <c r="S128" s="22" t="n">
+      <c r="I128" s="22" t="n">
+        <v>-45.591</v>
+      </c>
+      <c r="M128" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="V128" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" s="22" t="n">
+        <v>-45.591</v>
+      </c>
+      <c r="X128" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>Purchase Of Memberships Inv CF</t>
-        </is>
-      </c>
-      <c r="C129" s="22" t="n">
-        <v>0</v>
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="n">
+        <v>513.6660000000001</v>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v>1082.593</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>542.66</v>
+      </c>
+      <c r="I129" s="12" t="n">
+        <v>1148.987</v>
+      </c>
+      <c r="K129" s="12" t="n">
+        <v>585.807</v>
+      </c>
+      <c r="M129" s="12" t="n">
+        <v>1333.374</v>
+      </c>
+      <c r="O129" s="12" t="n">
+        <v>505.849</v>
+      </c>
+      <c r="P129" s="12" t="n">
+        <v>383.124</v>
+      </c>
+      <c r="Q129" s="12" t="n">
+        <v>643.008</v>
+      </c>
+      <c r="R129" s="12" t="n">
+        <v>609.727</v>
+      </c>
+      <c r="S129" s="12" t="n">
+        <v>675.571</v>
+      </c>
+      <c r="T129" s="12" t="n">
+        <v>985.125</v>
+      </c>
+      <c r="U129" s="12" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="V129" s="12" t="n">
+        <v>1082.593</v>
+      </c>
+      <c r="W129" s="12" t="n">
+        <v>1148.987</v>
+      </c>
+      <c r="X129" s="12" t="n">
+        <v>1333.374</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>임차보증금 납입</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="C130" s="22" t="n">
-        <v>-0.739</v>
+        <v>-1.6</v>
       </c>
       <c r="E130" s="22" t="n">
-        <v>-0.739</v>
+        <v>-1.797</v>
       </c>
       <c r="G130" s="22" t="n">
+        <v>-1.743</v>
+      </c>
+      <c r="I130" s="22" t="n">
+        <v>-3.173</v>
+      </c>
+      <c r="K130" s="22" t="n">
+        <v>-2.864</v>
+      </c>
+      <c r="M130" s="22" t="n">
+        <v>-4.075</v>
+      </c>
+      <c r="O130" s="22" t="n">
+        <v>-1.443</v>
+      </c>
+      <c r="P130" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I130" s="22" t="n">
+      <c r="Q130" s="22" t="n">
+        <v>-1.537</v>
+      </c>
+      <c r="R130" s="22" t="n">
+        <v>-0.237</v>
+      </c>
+      <c r="S130" s="22" t="n">
+        <v>-7.487</v>
+      </c>
+      <c r="T130" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T130" s="22" t="n">
-        <v>-19.054</v>
-      </c>
       <c r="U130" s="22" t="n">
-        <v>-0.01</v>
+        <v>-11.778</v>
       </c>
       <c r="V130" s="22" t="n">
-        <v>-0.739</v>
+        <v>-1.797</v>
       </c>
       <c r="W130" s="22" t="n">
-        <v>0</v>
+        <v>-3.173</v>
+      </c>
+      <c r="X130" s="22" t="n">
+        <v>-4.075</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Golf Club Memberships Inv CF</t>
-        </is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="C131" s="22" t="n">
+        <v>-218.557</v>
       </c>
       <c r="E131" s="22" t="n">
-        <v>0</v>
+        <v>-448.281</v>
+      </c>
+      <c r="G131" s="22" t="n">
+        <v>-221.224</v>
+      </c>
+      <c r="I131" s="22" t="n">
+        <v>-451.285</v>
+      </c>
+      <c r="K131" s="22" t="n">
+        <v>-268.712</v>
+      </c>
+      <c r="M131" s="22" t="n">
+        <v>-541.332</v>
+      </c>
+      <c r="O131" s="22" t="n">
+        <v>-161.439</v>
+      </c>
+      <c r="P131" s="22" t="n">
+        <v>-143.21</v>
+      </c>
+      <c r="Q131" s="22" t="n">
+        <v>-128.894</v>
+      </c>
+      <c r="R131" s="22" t="n">
+        <v>-207.595</v>
+      </c>
+      <c r="S131" s="22" t="n">
+        <v>-181.156</v>
       </c>
       <c r="T131" s="22" t="n">
-        <v>0</v>
+        <v>-199.425</v>
       </c>
       <c r="U131" s="22" t="n">
-        <v>-9.736000000000001</v>
+        <v>-335.02</v>
       </c>
       <c r="V131" s="22" t="n">
-        <v>0</v>
+        <v>-448.281</v>
+      </c>
+      <c r="W131" s="22" t="n">
+        <v>-451.285</v>
+      </c>
+      <c r="X131" s="22" t="n">
+        <v>-541.332</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>유가증권 취득</t>
-        </is>
-      </c>
-      <c r="I132" s="22" t="n">
+          <t>임차보증금·보증금 납입</t>
+        </is>
+      </c>
+      <c r="O132" s="22" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="P132" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="M132" s="22" t="n">
-        <v>-1990.616</v>
-      </c>
-      <c r="W132" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" s="22" t="n">
-        <v>-1990.616</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>임차보증금 회수</t>
-        </is>
-      </c>
-      <c r="G133" s="22" t="n">
+          <t>투자유가증권 취득</t>
+        </is>
+      </c>
+      <c r="Q133" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I133" s="22" t="n">
+      <c r="R133" s="22" t="n">
+        <v>-496.973</v>
+      </c>
+      <c r="S133" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="K133" s="22" t="n">
-        <v>52.432</v>
-      </c>
-      <c r="M133" s="22" t="n">
-        <v>52.432</v>
-      </c>
-      <c r="W133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" s="22" t="n">
-        <v>52.432</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C134" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="22" t="n">
-        <v>-1.079</v>
-      </c>
-      <c r="M134" s="22" t="n">
-        <v>-0.479</v>
-      </c>
-      <c r="O134" s="22" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P134" s="22" t="n">
-        <v>0</v>
+          <t>투자유가증권 매각</t>
+        </is>
       </c>
       <c r="Q134" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R134" s="22" t="n">
-        <v>-0.001</v>
+        <v>516.402</v>
       </c>
       <c r="S134" s="22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T134" s="22" t="n">
-        <v>-0.183</v>
-      </c>
-      <c r="U134" s="22" t="n">
-        <v>0.183</v>
-      </c>
-      <c r="V134" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="W134" s="22" t="n">
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>Purchase Of Memberships Inv CF</t>
+        </is>
+      </c>
+      <c r="C135" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="X134" s="22" t="n">
-        <v>-0.479</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C135" s="12" t="n">
-        <v>-220.897</v>
-      </c>
-      <c r="E135" s="12" t="n">
-        <v>-450.819</v>
-      </c>
-      <c r="G135" s="12" t="n">
-        <v>-222.968</v>
-      </c>
-      <c r="I135" s="12" t="n">
-        <v>-454.458</v>
-      </c>
-      <c r="K135" s="12" t="n">
-        <v>-220.223</v>
-      </c>
-      <c r="M135" s="12" t="n">
-        <v>-2484.071</v>
-      </c>
-      <c r="O135" s="12" t="n">
-        <v>-162.883</v>
-      </c>
-      <c r="P135" s="12" t="n">
-        <v>-143.21</v>
-      </c>
-      <c r="Q135" s="12" t="n">
-        <v>-130.432</v>
-      </c>
-      <c r="R135" s="12" t="n">
-        <v>-188.405</v>
-      </c>
-      <c r="S135" s="12" t="n">
-        <v>-188.344</v>
-      </c>
-      <c r="T135" s="12" t="n">
-        <v>-218.663</v>
-      </c>
-      <c r="U135" s="12" t="n">
-        <v>-356.36</v>
-      </c>
-      <c r="V135" s="12" t="n">
-        <v>-450.819</v>
-      </c>
-      <c r="W135" s="12" t="n">
-        <v>-454.458</v>
-      </c>
-      <c r="X135" s="12" t="n">
-        <v>-2484.071</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
-        </is>
-      </c>
-      <c r="O136" s="22" t="n">
-        <v>331.2</v>
-      </c>
-      <c r="P136" s="22" t="n">
+          <t>임차보증금 납입</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="n">
+        <v>-0.739</v>
+      </c>
+      <c r="E136" s="22" t="n">
+        <v>-0.739</v>
+      </c>
+      <c r="G136" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" s="22" t="n">
-        <v>672.396</v>
-      </c>
-      <c r="R136" s="22" t="n">
+      <c r="I136" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" s="22" t="n">
+        <v>-19.054</v>
+      </c>
+      <c r="U136" s="22" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V136" s="22" t="n">
+        <v>-0.739</v>
+      </c>
+      <c r="W136" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
-        </is>
-      </c>
-      <c r="C137" s="22" t="n">
-        <v>0</v>
+          <t>Purchase Of Golf Club Memberships Inv CF</t>
+        </is>
       </c>
       <c r="E137" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" s="22" t="n">
-        <v>-0.047</v>
-      </c>
-      <c r="P137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" s="22" t="n">
-        <v>-0.052</v>
-      </c>
-      <c r="R137" s="22" t="n">
-        <v>-0.055</v>
-      </c>
-      <c r="S137" s="22" t="n">
-        <v>-0.19</v>
-      </c>
       <c r="T137" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U137" s="22" t="n">
-        <v>-0.099</v>
+        <v>-9.736000000000001</v>
       </c>
       <c r="V137" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="W137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" s="22" t="n">
-        <v>-0.047</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>스톡옵션 행사 수입</t>
-        </is>
-      </c>
-      <c r="C138" s="22" t="n">
+          <t>유가증권 취득</t>
+        </is>
+      </c>
+      <c r="I138" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E138" s="22" t="n">
+      <c r="M138" s="22" t="n">
+        <v>-1990.616</v>
+      </c>
+      <c r="W138" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O138" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" s="22" t="n">
-        <v>27.888</v>
-      </c>
-      <c r="Q138" s="22" t="n">
-        <v>6.132</v>
-      </c>
-      <c r="R138" s="22" t="n">
-        <v>4.032</v>
-      </c>
-      <c r="S138" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" s="22" t="n">
-        <v>0.924</v>
-      </c>
-      <c r="U138" s="22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V138" s="22" t="n">
-        <v>0</v>
+      <c r="X138" s="22" t="n">
+        <v>-1990.616</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용 지출</t>
-        </is>
-      </c>
-      <c r="O139" s="22" t="n">
-        <v>-10.162</v>
-      </c>
-      <c r="P139" s="22" t="n">
+          <t>임차보증금 회수</t>
+        </is>
+      </c>
+      <c r="G139" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" s="22" t="n">
-        <v>-10.073</v>
-      </c>
-      <c r="R139" s="22" t="n">
-        <v>-15.583</v>
-      </c>
-      <c r="S139" s="22" t="n">
+      <c r="I139" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="K139" s="22" t="n">
+        <v>52.432</v>
+      </c>
+      <c r="M139" s="22" t="n">
+        <v>52.432</v>
+      </c>
+      <c r="W139" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" s="22" t="n">
+        <v>52.432</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C140" s="22" t="n">
-        <v>-89.776</v>
+        <v>0</v>
       </c>
       <c r="E140" s="22" t="n">
-        <v>-187.148</v>
+        <v>0</v>
       </c>
       <c r="G140" s="22" t="n">
-        <v>-97.29900000000001</v>
+        <v>0</v>
       </c>
       <c r="I140" s="22" t="n">
-        <v>-217.076</v>
+        <v>0</v>
       </c>
       <c r="K140" s="22" t="n">
-        <v>-119.781</v>
+        <v>-1.079</v>
       </c>
       <c r="M140" s="22" t="n">
-        <v>-247.006</v>
+        <v>-0.479</v>
       </c>
       <c r="O140" s="22" t="n">
-        <v>-87</v>
+        <v>0.001</v>
       </c>
       <c r="P140" s="22" t="n">
-        <v>-96.434</v>
+        <v>0</v>
       </c>
       <c r="Q140" s="22" t="n">
-        <v>-72.598</v>
+        <v>0</v>
       </c>
       <c r="R140" s="22" t="n">
-        <v>-100.532</v>
+        <v>-0.001</v>
       </c>
       <c r="S140" s="22" t="n">
-        <v>-134.4</v>
+        <v>0.3</v>
       </c>
       <c r="T140" s="22" t="n">
-        <v>-156.877</v>
+        <v>-0.183</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>-172.185</v>
+        <v>0.183</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>-187.148</v>
+        <v>0</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>-217.076</v>
+        <v>0</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>-247.006</v>
+        <v>-0.479</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>재무활동 현금흐름</t>
+          <t>투자활동 현금흐름</t>
         </is>
       </c>
       <c r="C141" s="12" t="n">
-        <v>-89.776</v>
+        <v>-220.897</v>
       </c>
       <c r="E141" s="12" t="n">
-        <v>-187.148</v>
+        <v>-450.819</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>-97.29900000000001</v>
+        <v>-222.968</v>
       </c>
       <c r="I141" s="12" t="n">
-        <v>-217.076</v>
+        <v>-454.458</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>-119.781</v>
+        <v>-220.223</v>
       </c>
       <c r="M141" s="12" t="n">
-        <v>-247.053</v>
+        <v>-2484.071</v>
       </c>
       <c r="O141" s="12" t="n">
-        <v>234.037</v>
+        <v>-162.883</v>
       </c>
       <c r="P141" s="12" t="n">
-        <v>-68.54600000000001</v>
+        <v>-143.21</v>
       </c>
       <c r="Q141" s="12" t="n">
-        <v>595.803</v>
+        <v>-130.432</v>
       </c>
       <c r="R141" s="12" t="n">
-        <v>-112.139</v>
+        <v>-188.405</v>
       </c>
       <c r="S141" s="12" t="n">
-        <v>-134.591</v>
+        <v>-188.344</v>
       </c>
       <c r="T141" s="12" t="n">
-        <v>-155.953</v>
+        <v>-218.663</v>
       </c>
       <c r="U141" s="12" t="n">
-        <v>-171.024</v>
+        <v>-356.36</v>
       </c>
       <c r="V141" s="12" t="n">
-        <v>-187.148</v>
+        <v>-450.819</v>
       </c>
       <c r="W141" s="12" t="n">
-        <v>-217.076</v>
+        <v>-454.458</v>
       </c>
       <c r="X141" s="12" t="n">
-        <v>-247.053</v>
+        <v>-2484.071</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="O142" s="22" t="n">
+        <v>331.2</v>
+      </c>
+      <c r="P142" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="22" t="n">
+        <v>672.396</v>
+      </c>
+      <c r="R142" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="C143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="22" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="P143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" s="22" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="R143" s="22" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="S143" s="22" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="T143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" s="22" t="n">
+        <v>-0.099</v>
+      </c>
+      <c r="V143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" s="22" t="n">
+        <v>-0.047</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20" t="inlineStr">
+        <is>
+          <t>스톡옵션 행사 수입</t>
+        </is>
+      </c>
+      <c r="C144" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" s="22" t="n">
+        <v>27.888</v>
+      </c>
+      <c r="Q144" s="22" t="n">
+        <v>6.132</v>
+      </c>
+      <c r="R144" s="22" t="n">
+        <v>4.032</v>
+      </c>
+      <c r="S144" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" s="22" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="U144" s="22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V144" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="20" t="inlineStr">
+        <is>
+          <t>상장 관련 비용 지출</t>
+        </is>
+      </c>
+      <c r="O145" s="22" t="n">
+        <v>-10.162</v>
+      </c>
+      <c r="P145" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="22" t="n">
+        <v>-10.073</v>
+      </c>
+      <c r="R145" s="22" t="n">
+        <v>-15.583</v>
+      </c>
+      <c r="S145" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="C146" s="22" t="n">
+        <v>-89.776</v>
+      </c>
+      <c r="E146" s="22" t="n">
+        <v>-187.148</v>
+      </c>
+      <c r="G146" s="22" t="n">
+        <v>-97.29900000000001</v>
+      </c>
+      <c r="I146" s="22" t="n">
+        <v>-217.076</v>
+      </c>
+      <c r="K146" s="22" t="n">
+        <v>-119.781</v>
+      </c>
+      <c r="M146" s="22" t="n">
+        <v>-247.006</v>
+      </c>
+      <c r="O146" s="22" t="n">
+        <v>-87</v>
+      </c>
+      <c r="P146" s="22" t="n">
+        <v>-96.434</v>
+      </c>
+      <c r="Q146" s="22" t="n">
+        <v>-72.598</v>
+      </c>
+      <c r="R146" s="22" t="n">
+        <v>-100.532</v>
+      </c>
+      <c r="S146" s="22" t="n">
+        <v>-134.4</v>
+      </c>
+      <c r="T146" s="22" t="n">
+        <v>-156.877</v>
+      </c>
+      <c r="U146" s="22" t="n">
+        <v>-172.185</v>
+      </c>
+      <c r="V146" s="22" t="n">
+        <v>-187.148</v>
+      </c>
+      <c r="W146" s="22" t="n">
+        <v>-217.076</v>
+      </c>
+      <c r="X146" s="22" t="n">
+        <v>-247.006</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="n">
+        <v>-89.776</v>
+      </c>
+      <c r="E147" s="12" t="n">
+        <v>-187.148</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>-97.29900000000001</v>
+      </c>
+      <c r="I147" s="12" t="n">
+        <v>-217.076</v>
+      </c>
+      <c r="K147" s="12" t="n">
+        <v>-119.781</v>
+      </c>
+      <c r="M147" s="12" t="n">
+        <v>-247.053</v>
+      </c>
+      <c r="O147" s="12" t="n">
+        <v>234.037</v>
+      </c>
+      <c r="P147" s="12" t="n">
+        <v>-68.54600000000001</v>
+      </c>
+      <c r="Q147" s="12" t="n">
+        <v>595.803</v>
+      </c>
+      <c r="R147" s="12" t="n">
+        <v>-112.139</v>
+      </c>
+      <c r="S147" s="12" t="n">
+        <v>-134.591</v>
+      </c>
+      <c r="T147" s="12" t="n">
+        <v>-155.953</v>
+      </c>
+      <c r="U147" s="12" t="n">
+        <v>-171.024</v>
+      </c>
+      <c r="V147" s="12" t="n">
+        <v>-187.148</v>
+      </c>
+      <c r="W147" s="12" t="n">
+        <v>-217.076</v>
+      </c>
+      <c r="X147" s="12" t="n">
+        <v>-247.053</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="C142" s="22" t="n">
+      <c r="C148" s="22" t="n">
         <v>202.991</v>
       </c>
-      <c r="E142" s="22" t="n">
+      <c r="E148" s="22" t="n">
         <v>444.625</v>
       </c>
-      <c r="G142" s="22" t="n">
+      <c r="G148" s="22" t="n">
         <v>222.392</v>
       </c>
-      <c r="I142" s="22" t="n">
+      <c r="I148" s="22" t="n">
         <v>477.452</v>
       </c>
-      <c r="K142" s="22" t="n">
+      <c r="K148" s="22" t="n">
         <v>245.801</v>
       </c>
-      <c r="M142" s="22" t="n">
+      <c r="M148" s="22" t="n">
         <v>-1397.75</v>
       </c>
-      <c r="O142" s="22" t="n">
+      <c r="O148" s="22" t="n">
         <v>577.003</v>
       </c>
-      <c r="P142" s="22" t="n">
+      <c r="P148" s="22" t="n">
         <v>171.367</v>
       </c>
-      <c r="Q142" s="22" t="n">
+      <c r="Q148" s="22" t="n">
         <v>1108.379</v>
       </c>
-      <c r="R142" s="22" t="n">
+      <c r="R148" s="22" t="n">
         <v>309.182</v>
       </c>
-      <c r="S142" s="22" t="n">
+      <c r="S148" s="22" t="n">
         <v>352.636</v>
       </c>
-      <c r="T142" s="22" t="n">
+      <c r="T148" s="22" t="n">
         <v>610.508</v>
       </c>
-      <c r="U142" s="22" t="n">
+      <c r="U148" s="22" t="n">
         <v>302.414</v>
       </c>
-      <c r="V142" s="22" t="n">
+      <c r="V148" s="22" t="n">
         <v>444.625</v>
       </c>
-      <c r="W142" s="22" t="n">
+      <c r="W148" s="22" t="n">
         <v>477.452</v>
       </c>
-      <c r="X142" s="22" t="n">
+      <c r="X148" s="22" t="n">
         <v>-1397.75</v>
       </c>
     </row>
@@ -8484,7 +8891,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -9860,7 +10267,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -9912,7 +10319,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -9964,7 +10371,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -10016,7 +10423,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -10068,7 +10475,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -10120,7 +10527,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -10172,7 +10579,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -10182,43 +10589,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -10242,7 +10649,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -10294,7 +10701,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -10346,7 +10753,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -10398,7 +10805,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -10450,7 +10857,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -10502,7 +10909,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -10572,7 +10979,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -10624,7 +11031,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -10634,49 +11041,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -10686,49 +11093,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -10738,49 +11145,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -10790,43 +11197,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -10850,7 +11257,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -10902,7 +11309,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -10954,7 +11361,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -11006,7 +11413,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -12803,24 +13210,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>

--- a/docs/data/jp/xlsx/3969.xlsx
+++ b/docs/data/jp/xlsx/3969.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재무상태표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터 데이터" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'연간'!$3:$3</definedName>
@@ -21,14 +22,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;;-0.0&quot;x&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;년&quot;;-0.0&quot;년&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0&quot;일&quot;;-0&quot;일&quot;;&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0;\(#,##0.0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,11 +128,31 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -155,6 +177,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -345,7 +372,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9088,7 +9130,7 @@
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>Payments Of Head Office Relocation Expenses Ope CF</t>
+          <t>본사 이전비용 지급액</t>
         </is>
       </c>
       <c r="D139" s="22" t="n">
@@ -9354,7 +9396,7 @@
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Golf Club Memberships Inv CF</t>
+          <t>골프 회원권 취득 지출</t>
         </is>
       </c>
       <c r="D147" s="22" t="n">
@@ -14190,6 +14232,706 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>에이트레드 섹터·사업 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>상반기 fy27</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="C6" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>매출 YoY</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>gp</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="n">
+        <v>10.61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="56" t="inlineStr">
+        <is>
+          <t>sga</t>
+        </is>
+      </c>
+      <c r="B9" s="57" t="n">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B10" s="57" t="n">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="56" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="B11" s="57" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="56" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="B12" s="57" t="n">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="56" t="inlineStr">
+        <is>
+          <t>ord YoY</t>
+        </is>
+      </c>
+      <c r="B13" s="57" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B14" s="57" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="56" t="inlineStr">
+        <is>
+          <t>순이익 YoY</t>
+        </is>
+      </c>
+      <c r="B15" s="57" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B16" s="57" t="n">
+        <v>50.22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="54" t="inlineStr">
+        <is>
+          <t>상반기 fy27 · 계획 상반기</t>
+        </is>
+      </c>
+      <c r="B18" s="54" t="n"/>
+      <c r="C18" s="54" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B20" s="57" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="C20" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B21" s="57" t="n">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B22" s="57" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="54" t="inlineStr">
+        <is>
+          <t>2Q single calc</t>
+        </is>
+      </c>
+      <c r="B24" s="54" t="n"/>
+      <c r="C24" s="54" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C25" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B26" s="57" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="C26" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="56" t="inlineStr">
+        <is>
+          <t>매출 YoY</t>
+        </is>
+      </c>
+      <c r="B27" s="57" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="56" t="inlineStr">
+        <is>
+          <t>gp</t>
+        </is>
+      </c>
+      <c r="B28" s="57" t="n">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="56" t="inlineStr">
+        <is>
+          <t>매출총이익률</t>
+        </is>
+      </c>
+      <c r="B29" s="57" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="56" t="inlineStr">
+        <is>
+          <t>sga</t>
+        </is>
+      </c>
+      <c r="B30" s="57" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B31" s="57" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="56" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="B32" s="57" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="56" t="inlineStr">
+        <is>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="B33" s="57" t="n">
+        <v>35.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B34" s="57" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="56" t="inlineStr">
+        <is>
+          <t>순이익 YoY</t>
+        </is>
+      </c>
+      <c r="B35" s="57" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="56" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="B36" s="57" t="n">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="56" t="inlineStr">
+        <is>
+          <t>cloud YoY</t>
+        </is>
+      </c>
+      <c r="B37" s="57" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="56" t="inlineStr">
+        <is>
+          <t>cloud QoQ add</t>
+        </is>
+      </c>
+      <c r="B38" s="57" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="56" t="inlineStr">
+        <is>
+          <t>aw</t>
+        </is>
+      </c>
+      <c r="B39" s="57" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="56" t="inlineStr">
+        <is>
+          <t>aw YoY</t>
+        </is>
+      </c>
+      <c r="B40" s="57" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="56" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+      <c r="B41" s="57" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="56" t="inlineStr">
+        <is>
+          <t>xp YoY</t>
+        </is>
+      </c>
+      <c r="B42" s="57" t="n">
+        <v>-23.9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="54" t="inlineStr">
+        <is>
+          <t>2Q single calc · implied 계획 2q</t>
+        </is>
+      </c>
+      <c r="B44" s="54" t="n"/>
+      <c r="C44" s="54" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B45" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C45" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B46" s="57" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="C46" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B47" s="57" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="54" t="inlineStr">
+        <is>
+          <t>가이던스 fy27</t>
+        </is>
+      </c>
+      <c r="B49" s="54" t="n"/>
+      <c r="C49" s="54" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B50" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C50" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B51" s="57" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="C51" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B52" s="57" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="56" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="B53" s="57" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B54" s="57" t="n">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B55" s="57" t="n">
+        <v>104.58</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="56" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B56" s="59" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="54" t="inlineStr">
+        <is>
+          <t>가이던스 fy27 · 하반기 implied</t>
+        </is>
+      </c>
+      <c r="B58" s="54" t="n"/>
+      <c r="C58" s="54" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B59" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C59" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B60" s="57" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="C60" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="56" t="inlineStr">
+        <is>
+          <t>매출 YoY</t>
+        </is>
+      </c>
+      <c r="B61" s="57" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B62" s="57" t="n">
+        <v>6.13</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="56" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="B63" s="57" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="54" t="inlineStr">
+        <is>
+          <t>preview · ours 2q</t>
+        </is>
+      </c>
+      <c r="B65" s="54" t="n"/>
+      <c r="C65" s="54" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B66" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C66" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B67" s="57" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="C67" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B68" s="57" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14206,17 +14948,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="53" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
